--- a/clustering/sepsectors/patterns.xlsx
+++ b/clustering/sepsectors/patterns.xlsx
@@ -4,19 +4,20 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
   </bookViews>
   <sheets>
     <sheet name="Pattern best" sheetId="1" r:id="rId1"/>
     <sheet name="Pattern worst" sheetId="2" r:id="rId2"/>
+    <sheet name="best|worst" sheetId="3" r:id="rId3"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId3"/>
     <externalReference r:id="rId4"/>
     <externalReference r:id="rId5"/>
     <externalReference r:id="rId6"/>
     <externalReference r:id="rId7"/>
     <externalReference r:id="rId8"/>
+    <externalReference r:id="rId9"/>
   </externalReferences>
   <calcPr calcId="162913"/>
   <extLst>
@@ -721,7 +722,10 @@
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:schemeClr val="bg1"/>
+      <a:schemeClr val="accent6">
+        <a:lumMod val="40000"/>
+        <a:lumOff val="60000"/>
+      </a:schemeClr>
     </a:solidFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
@@ -1397,7 +1401,10 @@
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:schemeClr val="bg1"/>
+      <a:schemeClr val="accent6">
+        <a:lumMod val="40000"/>
+        <a:lumOff val="60000"/>
+      </a:schemeClr>
     </a:solidFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
@@ -1693,7 +1700,9 @@
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:spPr>
-        <a:noFill/>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
         <a:ln>
           <a:noFill/>
         </a:ln>
@@ -2411,7 +2420,10 @@
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:schemeClr val="bg1"/>
+      <a:schemeClr val="accent6">
+        <a:lumMod val="40000"/>
+        <a:lumOff val="60000"/>
+      </a:schemeClr>
     </a:solidFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
@@ -5446,7 +5458,10 @@
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:schemeClr val="bg1"/>
+      <a:schemeClr val="accent6">
+        <a:lumMod val="40000"/>
+        <a:lumOff val="60000"/>
+      </a:schemeClr>
     </a:solidFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
@@ -5783,7 +5798,10 @@
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:schemeClr val="bg1"/>
+      <a:schemeClr val="accent6">
+        <a:lumMod val="40000"/>
+        <a:lumOff val="60000"/>
+      </a:schemeClr>
     </a:solidFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
@@ -6457,7 +6475,10 @@
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:schemeClr val="bg1"/>
+      <a:schemeClr val="accent6">
+        <a:lumMod val="40000"/>
+        <a:lumOff val="60000"/>
+      </a:schemeClr>
     </a:solidFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
@@ -7131,7 +7152,10 @@
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:schemeClr val="bg1"/>
+      <a:schemeClr val="accent6">
+        <a:lumMod val="40000"/>
+        <a:lumOff val="60000"/>
+      </a:schemeClr>
     </a:solidFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
@@ -8142,7 +8166,10 @@
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:schemeClr val="bg1"/>
+      <a:schemeClr val="accent2">
+        <a:lumMod val="40000"/>
+        <a:lumOff val="60000"/>
+      </a:schemeClr>
     </a:solidFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
@@ -8817,7 +8844,10 @@
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:schemeClr val="bg1"/>
+      <a:schemeClr val="accent2">
+        <a:lumMod val="40000"/>
+        <a:lumOff val="60000"/>
+      </a:schemeClr>
     </a:solidFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
@@ -10507,7 +10537,10 @@
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:schemeClr val="bg1"/>
+      <a:schemeClr val="accent2">
+        <a:lumMod val="40000"/>
+        <a:lumOff val="60000"/>
+      </a:schemeClr>
     </a:solidFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
@@ -12533,7 +12566,10 @@
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:schemeClr val="bg1"/>
+      <a:schemeClr val="accent2">
+        <a:lumMod val="40000"/>
+        <a:lumOff val="60000"/>
+      </a:schemeClr>
     </a:solidFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
@@ -12871,7 +12907,10 @@
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:schemeClr val="bg1"/>
+      <a:schemeClr val="accent2">
+        <a:lumMod val="40000"/>
+        <a:lumOff val="60000"/>
+      </a:schemeClr>
     </a:solidFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
@@ -13547,7 +13586,10 @@
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:schemeClr val="bg1"/>
+      <a:schemeClr val="accent2">
+        <a:lumMod val="40000"/>
+        <a:lumOff val="60000"/>
+      </a:schemeClr>
     </a:solidFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
@@ -13884,7 +13926,10 @@
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:schemeClr val="bg1"/>
+      <a:schemeClr val="accent2">
+        <a:lumMod val="40000"/>
+        <a:lumOff val="60000"/>
+      </a:schemeClr>
     </a:solidFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
@@ -15570,7 +15615,10 @@
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:schemeClr val="bg1"/>
+      <a:schemeClr val="accent2">
+        <a:lumMod val="40000"/>
+        <a:lumOff val="60000"/>
+      </a:schemeClr>
     </a:solidFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
@@ -17255,7 +17303,10 @@
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:schemeClr val="bg1"/>
+      <a:schemeClr val="accent2">
+        <a:lumMod val="40000"/>
+        <a:lumOff val="60000"/>
+      </a:schemeClr>
     </a:solidFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
@@ -17434,6 +17485,1241 @@
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-DF31-44A8-B3A6-806521096E25}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="744722240"/>
+        <c:axId val="744723072"/>
+      </c:radarChart>
+      <c:catAx>
+        <c:axId val="744722240"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="744723072"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="744723072"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="744722240"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart57.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:effectLst/>
+              </a:rPr>
+              <a:t>25</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:radarChart>
+        <c:radarStyle val="marker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>[2]Original!$C$262</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0,717493619</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>[2]Original!$D$113:$G$113</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Year</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>[2]Original!$D$262:$G$262</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8.7621696860402221E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3.3414603489272977E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-7C86-43E2-819C-0FC85042D463}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>[2]Original!$C$265</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>[2]Original!$D$113:$G$113</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Year</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>[2]Original!$D$265:$G$265</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.93878727817122176</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.34445526276978805</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-7C86-43E2-819C-0FC85042D463}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="744722240"/>
+        <c:axId val="744723072"/>
+      </c:radarChart>
+      <c:catAx>
+        <c:axId val="744722240"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="744723072"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="744723072"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="744722240"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart58.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:effectLst/>
+              </a:rPr>
+              <a:t>26</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:radarChart>
+        <c:radarStyle val="marker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>[2]Original!$C$287</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0,69712943</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>[2]Original!$D$113:$G$113</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Year</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>[2]Original!$D$287:$G$287</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.49019879906061425</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7.571057460945764E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8.6332237253377908E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-6DFE-4879-AA31-6F6E1A830CE2}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>[2]Original!$C$290</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>[2]Original!$D$113:$G$113</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Year</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>[2]Original!$D$290:$G$290</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.4287191813565403</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.53569574699465849</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9.5790129052906028E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-6DFE-4879-AA31-6F6E1A830CE2}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="744722240"/>
+        <c:axId val="744723072"/>
+      </c:radarChart>
+      <c:catAx>
+        <c:axId val="744722240"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="744723072"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="744723072"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="744722240"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="accent6">
+        <a:lumMod val="40000"/>
+        <a:lumOff val="60000"/>
+      </a:schemeClr>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart59.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:effectLst/>
+              </a:rPr>
+              <a:t>52</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:radarChart>
+        <c:radarStyle val="marker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>[3]Sheet1!$C$65</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0,840499239</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>[3]Sheet1!$D$40:$G$40</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Year</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>[3]Sheet1!$D$65:$G$65</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.35996805668422921</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.8023291899267978E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-4DB0-4CC0-A9B6-C4EB59917A2B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>[3]Sheet1!$C$68</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>[3]Sheet1!$D$40:$G$40</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Year</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>[3]Sheet1!$D$68:$G$68</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.48600285522899472</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.33371170448451204</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.13268292211489857</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-4DB0-4CC0-A9B6-C4EB59917A2B}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -17772,6 +19058,1239 @@
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-C1D9-4F8D-B17D-5E890878913D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="744722240"/>
+        <c:axId val="744723072"/>
+      </c:radarChart>
+      <c:catAx>
+        <c:axId val="744722240"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="744723072"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="744723072"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="744722240"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart60.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:effectLst/>
+              </a:rPr>
+              <a:t>47</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:radarChart>
+        <c:radarStyle val="marker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>[6]Sheet1!$C$90</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0,883584262</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>[6]Sheet1!$D$39:$G$39</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Year</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>[6]Sheet1!$D$90:$G$90</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.10170195406656198</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.36473888253774922</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-9532-4A59-AF13-57125129C738}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>[6]Sheet1!$C$93</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>[6]Sheet1!$D$39:$G$39</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Year</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>[6]Sheet1!$D$93:$G$93</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.68281070033420188</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.67618318135157551</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.59090610893852613</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-9532-4A59-AF13-57125129C738}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="744722240"/>
+        <c:axId val="744723072"/>
+      </c:radarChart>
+      <c:catAx>
+        <c:axId val="744722240"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="744723072"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="744723072"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="744722240"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="accent6">
+        <a:lumMod val="40000"/>
+        <a:lumOff val="60000"/>
+      </a:schemeClr>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart61.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:effectLst/>
+              </a:rPr>
+              <a:t>73</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:radarChart>
+        <c:radarStyle val="marker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>[5]Sheet1!$C$94</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0,802585988</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>[5]Sheet1!$D$67:$G$67</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Year</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>[5]Sheet1!$D$94:$G$94</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.8578905609577977E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.10644850180398349</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-2FBA-4775-9010-61D512CD9896}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>[5]Sheet1!$C$97</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>[5]Sheet1!$D$67:$G$67</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Year</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>[5]Sheet1!$D$97:$G$97</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.75202719892054226</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3.5266868505225042E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-2FBA-4775-9010-61D512CD9896}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="744722240"/>
+        <c:axId val="744723072"/>
+      </c:radarChart>
+      <c:catAx>
+        <c:axId val="744722240"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="744723072"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="744723072"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="744722240"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart62.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:effectLst/>
+              </a:rPr>
+              <a:t>07</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:radarChart>
+        <c:radarStyle val="marker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>[4]Sheet1!$C$68</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0,636869588</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>[4]Sheet1!$D$43:$G$43</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Year</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>[4]Sheet1!$D$68:$G$68</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.28945244686889443</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.46185888639215267</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-2AEC-4E6A-9239-AD0491C00B06}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>[4]Sheet1!$C$71</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="7030A0"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>[4]Sheet1!$D$43:$G$43</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Year</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>ITcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>skvozcosts_s</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>trainingcosts_s</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>[4]Sheet1!$D$71:$G$71</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.98567037422891113</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.42098304385739743</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-2AEC-4E6A-9239-AD0491C00B06}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -21055,7 +23574,247 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors57.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors58.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors59.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/colors6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors60.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors61.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors62.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -47475,7 +50234,3037 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style57.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="317">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style58.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="317">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style59.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="317">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="317">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style60.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="317">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style61.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="317">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style62.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="317">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -51297,6 +57086,203 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>435614</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>58636</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>512900</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>3915</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Диаграмма 1"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>225879</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>76509</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>43</xdr:col>
+      <xdr:colOff>303164</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>21788</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Диаграмма 2"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>43</xdr:col>
+      <xdr:colOff>452438</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>52</xdr:col>
+      <xdr:colOff>508830</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>183404</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Диаграмма 3"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>71</xdr:col>
+      <xdr:colOff>500063</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>80</xdr:col>
+      <xdr:colOff>356417</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>183404</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Диаграмма 4"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>62</xdr:col>
+      <xdr:colOff>357188</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>71</xdr:col>
+      <xdr:colOff>318687</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>135779</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name="Диаграмма 5"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>53</xdr:col>
+      <xdr:colOff>214313</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>166688</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>62</xdr:col>
+      <xdr:colOff>64482</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>111967</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="7" name="Диаграмма 6"/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
@@ -51440,6 +57426,156 @@
         <row r="89">
           <cell r="D89" t="str">
             <v>Year</v>
+          </cell>
+        </row>
+        <row r="113">
+          <cell r="D113" t="str">
+            <v>Year</v>
+          </cell>
+          <cell r="E113" t="str">
+            <v>ITcosts_s</v>
+          </cell>
+          <cell r="F113" t="str">
+            <v>skvozcosts_s</v>
+          </cell>
+          <cell r="G113" t="str">
+            <v>trainingcosts_s</v>
+          </cell>
+        </row>
+        <row r="262">
+          <cell r="C262">
+            <v>0.71749361857336225</v>
+          </cell>
+          <cell r="D262">
+            <v>0.25</v>
+          </cell>
+          <cell r="E262">
+            <v>1</v>
+          </cell>
+          <cell r="F262">
+            <v>8.7621696860402221E-2</v>
+          </cell>
+          <cell r="G262">
+            <v>3.3414603489272977E-2</v>
+          </cell>
+        </row>
+        <row r="263">
+          <cell r="C263">
+            <v>0.74339840698029691</v>
+          </cell>
+          <cell r="D263">
+            <v>0.5</v>
+          </cell>
+          <cell r="E263">
+            <v>0.37919583070757845</v>
+          </cell>
+          <cell r="F263">
+            <v>0.24604511227578876</v>
+          </cell>
+          <cell r="G263">
+            <v>5.0333919862687079E-2</v>
+          </cell>
+        </row>
+        <row r="264">
+          <cell r="C264">
+            <v>0.84942603960209995</v>
+          </cell>
+          <cell r="D264">
+            <v>0.75</v>
+          </cell>
+          <cell r="E264">
+            <v>0.69088738020157991</v>
+          </cell>
+          <cell r="F264">
+            <v>1</v>
+          </cell>
+          <cell r="G264">
+            <v>5.6818716744632944E-2</v>
+          </cell>
+        </row>
+        <row r="265">
+          <cell r="C265">
+            <v>1</v>
+          </cell>
+          <cell r="D265">
+            <v>1</v>
+          </cell>
+          <cell r="E265">
+            <v>0.93878727817122176</v>
+          </cell>
+          <cell r="F265">
+            <v>0.34445526276978805</v>
+          </cell>
+          <cell r="G265">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="287">
+          <cell r="C287">
+            <v>0.69712943030064645</v>
+          </cell>
+          <cell r="D287">
+            <v>0.25</v>
+          </cell>
+          <cell r="E287">
+            <v>0.49019879906061425</v>
+          </cell>
+          <cell r="F287">
+            <v>7.571057460945764E-2</v>
+          </cell>
+          <cell r="G287">
+            <v>8.6332237253377908E-2</v>
+          </cell>
+        </row>
+        <row r="288">
+          <cell r="C288">
+            <v>0.74801703981263812</v>
+          </cell>
+          <cell r="D288">
+            <v>0.5</v>
+          </cell>
+          <cell r="E288">
+            <v>1</v>
+          </cell>
+          <cell r="F288">
+            <v>2.9773689598128844E-2</v>
+          </cell>
+          <cell r="G288">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="289">
+          <cell r="C289">
+            <v>0.9229809392532492</v>
+          </cell>
+          <cell r="D289">
+            <v>0.75</v>
+          </cell>
+          <cell r="E289">
+            <v>0.3535920446884655</v>
+          </cell>
+          <cell r="F289">
+            <v>1</v>
+          </cell>
+          <cell r="G289">
+            <v>0.12486016719718387</v>
+          </cell>
+        </row>
+        <row r="290">
+          <cell r="C290">
+            <v>1</v>
+          </cell>
+          <cell r="D290">
+            <v>1</v>
+          </cell>
+          <cell r="E290">
+            <v>0.4287191813565403</v>
+          </cell>
+          <cell r="F290">
+            <v>0.53569574699465849</v>
+          </cell>
+          <cell r="G290">
+            <v>9.5790129052906028E-2</v>
           </cell>
         </row>
       </sheetData>
@@ -51743,23 +57879,6 @@
             <v>0.45477225885659545</v>
           </cell>
         </row>
-        <row r="93">
-          <cell r="C93">
-            <v>1</v>
-          </cell>
-          <cell r="D93">
-            <v>0.25</v>
-          </cell>
-          <cell r="E93">
-            <v>0.89882061387652312</v>
-          </cell>
-          <cell r="F93">
-            <v>0.17795127025264079</v>
-          </cell>
-          <cell r="G93">
-            <v>1</v>
-          </cell>
-        </row>
         <row r="113">
           <cell r="D113" t="str">
             <v>Year</v>
@@ -51791,23 +57910,6 @@
             <v>1</v>
           </cell>
         </row>
-        <row r="117">
-          <cell r="C117">
-            <v>1</v>
-          </cell>
-          <cell r="D117">
-            <v>0.5</v>
-          </cell>
-          <cell r="E117">
-            <v>0.75686804000192376</v>
-          </cell>
-          <cell r="F117">
-            <v>1</v>
-          </cell>
-          <cell r="G117">
-            <v>0.49718479540475113</v>
-          </cell>
-        </row>
         <row r="138">
           <cell r="C138">
             <v>0.80140650744605846</v>
@@ -51823,23 +57925,6 @@
           </cell>
           <cell r="G138">
             <v>0.20562583073637467</v>
-          </cell>
-        </row>
-        <row r="141">
-          <cell r="C141">
-            <v>1</v>
-          </cell>
-          <cell r="D141">
-            <v>0.5</v>
-          </cell>
-          <cell r="E141">
-            <v>0.56379755979405544</v>
-          </cell>
-          <cell r="F141">
-            <v>0.50828225173152997</v>
-          </cell>
-          <cell r="G141">
-            <v>0.37838843465697375</v>
           </cell>
         </row>
         <row r="162">
@@ -51859,23 +57944,6 @@
             <v>0.90726496435854909</v>
           </cell>
         </row>
-        <row r="165">
-          <cell r="C165">
-            <v>1</v>
-          </cell>
-          <cell r="D165">
-            <v>0.25</v>
-          </cell>
-          <cell r="E165">
-            <v>1</v>
-          </cell>
-          <cell r="F165">
-            <v>0.69842143423119296</v>
-          </cell>
-          <cell r="G165">
-            <v>0.27079088952453417</v>
-          </cell>
-        </row>
         <row r="187">
           <cell r="C187">
             <v>0.90935810743449375</v>
@@ -51891,23 +57959,6 @@
           </cell>
           <cell r="G187">
             <v>0.55344093952236229</v>
-          </cell>
-        </row>
-        <row r="190">
-          <cell r="C190">
-            <v>1</v>
-          </cell>
-          <cell r="D190">
-            <v>0.5</v>
-          </cell>
-          <cell r="E190">
-            <v>0.84040363200323998</v>
-          </cell>
-          <cell r="F190">
-            <v>1</v>
-          </cell>
-          <cell r="G190">
-            <v>0.22466253890066659</v>
           </cell>
         </row>
         <row r="212">
@@ -51927,23 +57978,6 @@
             <v>0.7592293002304622</v>
           </cell>
         </row>
-        <row r="215">
-          <cell r="C215">
-            <v>1</v>
-          </cell>
-          <cell r="D215">
-            <v>1</v>
-          </cell>
-          <cell r="E215">
-            <v>0.57664977093076919</v>
-          </cell>
-          <cell r="F215">
-            <v>0.77853736812744556</v>
-          </cell>
-          <cell r="G215">
-            <v>1</v>
-          </cell>
-        </row>
         <row r="237">
           <cell r="C237">
             <v>0.76628830414256921</v>
@@ -51959,23 +57993,6 @@
           </cell>
           <cell r="G237">
             <v>0.3535046285504449</v>
-          </cell>
-        </row>
-        <row r="240">
-          <cell r="C240">
-            <v>1</v>
-          </cell>
-          <cell r="D240">
-            <v>0.25</v>
-          </cell>
-          <cell r="E240">
-            <v>0.62244477507294493</v>
-          </cell>
-          <cell r="F240">
-            <v>0.83919206923346823</v>
-          </cell>
-          <cell r="G240">
-            <v>0.50155358560624896</v>
           </cell>
         </row>
         <row r="262">
@@ -51995,23 +58012,6 @@
             <v>3.3414603489272977E-2</v>
           </cell>
         </row>
-        <row r="265">
-          <cell r="C265">
-            <v>1</v>
-          </cell>
-          <cell r="D265">
-            <v>1</v>
-          </cell>
-          <cell r="E265">
-            <v>0.93878727817122176</v>
-          </cell>
-          <cell r="F265">
-            <v>0.34445526276978805</v>
-          </cell>
-          <cell r="G265">
-            <v>1</v>
-          </cell>
-        </row>
         <row r="287">
           <cell r="C287">
             <v>0.69712943030064645</v>
@@ -52027,23 +58027,6 @@
           </cell>
           <cell r="G287">
             <v>8.6332237253377908E-2</v>
-          </cell>
-        </row>
-        <row r="290">
-          <cell r="C290">
-            <v>1</v>
-          </cell>
-          <cell r="D290">
-            <v>1</v>
-          </cell>
-          <cell r="E290">
-            <v>0.4287191813565403</v>
-          </cell>
-          <cell r="F290">
-            <v>0.53569574699465849</v>
-          </cell>
-          <cell r="G290">
-            <v>9.5790129052906028E-2</v>
           </cell>
         </row>
         <row r="311">
@@ -52063,23 +58046,6 @@
             <v>1</v>
           </cell>
         </row>
-        <row r="314">
-          <cell r="C314">
-            <v>1</v>
-          </cell>
-          <cell r="D314">
-            <v>1</v>
-          </cell>
-          <cell r="E314">
-            <v>0.14350332523225146</v>
-          </cell>
-          <cell r="F314">
-            <v>0.55578650039264843</v>
-          </cell>
-          <cell r="G314">
-            <v>0.45346685151196658</v>
-          </cell>
-        </row>
         <row r="336">
           <cell r="C336">
             <v>0.64423928937651198</v>
@@ -52095,23 +58061,6 @@
           </cell>
           <cell r="G336">
             <v>0.52585818127499084</v>
-          </cell>
-        </row>
-        <row r="339">
-          <cell r="C339">
-            <v>1</v>
-          </cell>
-          <cell r="D339">
-            <v>1</v>
-          </cell>
-          <cell r="E339">
-            <v>1</v>
-          </cell>
-          <cell r="F339">
-            <v>6.6315361695601274E-2</v>
-          </cell>
-          <cell r="G339">
-            <v>1</v>
           </cell>
         </row>
         <row r="361">
@@ -52131,23 +58080,6 @@
             <v>0.798027260026964</v>
           </cell>
         </row>
-        <row r="364">
-          <cell r="C364">
-            <v>1</v>
-          </cell>
-          <cell r="D364">
-            <v>0.25</v>
-          </cell>
-          <cell r="E364">
-            <v>1</v>
-          </cell>
-          <cell r="F364">
-            <v>0.33245092784424229</v>
-          </cell>
-          <cell r="G364">
-            <v>1</v>
-          </cell>
-        </row>
         <row r="386">
           <cell r="C386">
             <v>0.84698859751328548</v>
@@ -52165,23 +58097,6 @@
             <v>0.40747667756532474</v>
           </cell>
         </row>
-        <row r="389">
-          <cell r="C389">
-            <v>1</v>
-          </cell>
-          <cell r="D389">
-            <v>1</v>
-          </cell>
-          <cell r="E389">
-            <v>1</v>
-          </cell>
-          <cell r="F389">
-            <v>0.57548795019413157</v>
-          </cell>
-          <cell r="G389">
-            <v>0.78245342731197487</v>
-          </cell>
-        </row>
         <row r="411">
           <cell r="C411">
             <v>0.93331352650149302</v>
@@ -52197,23 +58112,6 @@
           </cell>
           <cell r="G411">
             <v>0.27586813623884487</v>
-          </cell>
-        </row>
-        <row r="414">
-          <cell r="C414">
-            <v>1</v>
-          </cell>
-          <cell r="D414">
-            <v>0.25</v>
-          </cell>
-          <cell r="E414">
-            <v>0.91790681578047295</v>
-          </cell>
-          <cell r="F414">
-            <v>0.84158694771293341</v>
-          </cell>
-          <cell r="G414">
-            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -53001,4 +58899,14 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>